--- a/verification/cases/roundtrip/excel_tables/init.xlsx
+++ b/verification/cases/roundtrip/excel_tables/init.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{76FA09E3-ECF2-4388-9149-073203492054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="15120" windowHeight="8010"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExcelTable" sheetId="1" r:id="rId1"/>
@@ -13,7 +14,20 @@
     <definedName name="NonTable">ExcelTable!$A$1:$C$4</definedName>
     <definedName name="TableAsRangeName">TableName[#All]</definedName>
   </definedNames>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -41,8 +55,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,20 +89,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TableName" displayName="TableName" ref="G1:I4" totalsRowShown="0">
-  <autoFilter ref="G1:I4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TableName" displayName="TableName" ref="G1:I4" totalsRowShown="0">
+  <autoFilter ref="G1:I4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Name"/>
-    <tableColumn id="2" name="Age"/>
-    <tableColumn id="3" name="AgeGroup">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Age"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="AgeGroup">
       <calculatedColumnFormula>INT(H2/10)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -97,9 +119,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Larissa-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Larissa">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -137,7 +159,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Larissa">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -171,6 +193,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -205,9 +228,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Larissa">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -380,17 +404,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="8" width="11.42578125" customWidth="1"/>
+    <col min="1" max="8" width="11.44140625" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" customWidth="1"/>
-    <col min="11" max="16384" width="11.42578125" hidden="1"/>
+    <col min="10" max="10" width="11.44140625" customWidth="1"/>
+    <col min="11" max="16384" width="11.44140625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -410,7 +434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -432,7 +456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -454,7 +478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -476,10 +500,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9"/>
-    <row r="6" spans="1:9"/>
-    <row r="7" spans="1:9"/>
-    <row r="8" spans="1:9"/>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
